--- a/corrected-bank-specimens-for-user/07-umb/parsed-excel/UMB Cocoa Purchases main(1110005147028)- Sept 23 - parsed.xlsx
+++ b/corrected-bank-specimens-for-user/07-umb/parsed-excel/UMB Cocoa Purchases main(1110005147028)- Sept 23 - parsed.xlsx
@@ -430,7 +430,7 @@
         <v>Exported</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-07-08T16:17:01.195Z</v>
+        <v>2026-07-14T13:50:03.997Z</v>
       </c>
     </row>
     <row r="5">

--- a/corrected-bank-specimens-for-user/07-umb/parsed-excel/UMB Cocoa Purchases main(1110005147028)- Sept 23 - parsed.xlsx
+++ b/corrected-bank-specimens-for-user/07-umb/parsed-excel/UMB Cocoa Purchases main(1110005147028)- Sept 23 - parsed.xlsx
@@ -430,7 +430,7 @@
         <v>Exported</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-07-14T13:50:03.997Z</v>
+        <v>2026-07-17T19:29:57.764Z</v>
       </c>
     </row>
     <row r="5">
